--- a/results/Int All Data 0.5/Rando_2_permute.xlsx
+++ b/results/Int All Data 0.5/Rando_2_permute.xlsx
@@ -440,697 +440,697 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8989713952697781</v>
+        <v>0.8948972852216988</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8942960516730611</v>
+        <v>0.8959909669272983</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.892863386916614</v>
+        <v>0.8945583021708514</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.903646738866495</v>
+        <v>0.8952746345490749</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.903646738866495</v>
+        <v>0.8924093050361808</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.904702054295566</v>
+        <v>0.8981399640619688</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.904702054295566</v>
+        <v>0.900704676800544</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.904702054295566</v>
+        <v>0.9011203924044486</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.904702054295566</v>
+        <v>0.9129590597834005</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.910432713321354</v>
+        <v>0.922271380700306</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8996877276480015</v>
+        <v>0.922271380700306</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8996877276480015</v>
+        <v>0.9229877130785294</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8932407362439901</v>
+        <v>0.922271380700306</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8932407362439901</v>
+        <v>0.9190670681365645</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8907143897819436</v>
+        <v>0.9219323976494584</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8907143897819436</v>
+        <v>0.9208770822203876</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8889043756981205</v>
+        <v>0.9191054344130931</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8896207080763441</v>
+        <v>0.9248360934388811</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8896207080763441</v>
+        <v>0.9266461075227042</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8917697052110145</v>
+        <v>0.9406337720363265</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8889043756981205</v>
+        <v>0.946703414112962</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8867553785634501</v>
+        <v>0.945270749356515</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8884886600942159</v>
+        <v>0.916918071001894</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8892049924724394</v>
+        <v>0.916918071001894</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8889427419746492</v>
+        <v>0.9162017386236705</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8882264095964256</v>
+        <v>0.9162017386236705</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7376815113399058</v>
+        <v>0.9162017386236705</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7386984604924481</v>
+        <v>0.9176344033801175</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7483113981836724</v>
+        <v>0.9176344033801175</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7350721188868923</v>
+        <v>0.9208770822203876</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7311961536593657</v>
+        <v>0.9187280850857171</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7315351367102132</v>
+        <v>0.9007430430770725</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7336841338448836</v>
+        <v>0.899649361371473</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7336841338448836</v>
+        <v>0.90108202612792</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6236632509348745</v>
+        <v>0.9026681559904812</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6250959156913215</v>
+        <v>0.9066271672089747</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6250959156913215</v>
+        <v>0.9076441163615172</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6250959156913215</v>
+        <v>0.9067806323150891</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6212520033024137</v>
+        <v>0.9001481229663445</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6234010004370841</v>
+        <v>0.8905288718372104</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6177087076878248</v>
+        <v>0.8948268661065515</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6141270457967073</v>
+        <v>0.8965217813607886</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6177854402408819</v>
+        <v>0.8936564518478947</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6177854402408819</v>
+        <v>0.8829114661745423</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6199344373755524</v>
+        <v>0.8829114661745423</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6199344373755524</v>
+        <v>0.8868704773930358</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6165766597056966</v>
+        <v>0.882649215676752</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6165766597056966</v>
+        <v>0.8783128551308824</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6159754261570589</v>
+        <v>0.8783128551308824</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6213671021319994</v>
+        <v>0.8783128551308824</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6335063862852703</v>
+        <v>0.8786902044582585</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6260040794521878</v>
+        <v>0.8807687824777815</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6252877470739644</v>
+        <v>0.8803530668738769</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6338070030595891</v>
+        <v>0.8800140838230295</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6359943664707882</v>
+        <v>0.8803530668738769</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6223073187314846</v>
+        <v>0.8817089990772667</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6206124034772473</v>
+        <v>0.8795983682191248</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6419935894322762</v>
+        <v>0.8797901996017677</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6574139187023457</v>
+        <v>0.8815234811325336</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6715166820455539</v>
+        <v>0.8805065319799912</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6833553494245059</v>
+        <v>0.8805065319799912</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6878068087999611</v>
+        <v>0.8822781797872857</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6992681268515371</v>
+        <v>0.8819775630129669</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7036044873974067</v>
+        <v>0.8836724782672041</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7036044873974067</v>
+        <v>0.8836724782672041</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.707864115390219</v>
+        <v>0.8814083823029479</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7013020251566218</v>
+        <v>0.8821247146811714</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7057918508086056</v>
+        <v>0.8731960565295518</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7057918508086056</v>
+        <v>0.8731960565295518</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6932368510514302</v>
+        <v>0.8708231751736195</v>
       </c>
     </row>
     <row r="72">
@@ -1140,847 +1140,847 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6945160507017629</v>
+        <v>0.8862051381671604</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7037516390656112</v>
+        <v>0.8765154679228789</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.709028216210966</v>
+        <v>0.8750444368899033</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7061308338594532</v>
+        <v>0.6683891020348696</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7233995434898742</v>
+        <v>0.6675576708270604</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7233995434898742</v>
+        <v>0.6506279442474867</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7168563935700063</v>
+        <v>0.6530391918799476</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7022354426691273</v>
+        <v>0.6530391918799476</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.733754067310961</v>
+        <v>0.6548108396872421</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7323214025545142</v>
+        <v>0.5861133504929338</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6840070904764217</v>
+        <v>0.5861133504929338</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6873328153076587</v>
+        <v>0.5596474187751931</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6640265164392209</v>
+        <v>0.5589310863969695</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6223063474333447</v>
+        <v>0.5367247826720412</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6234447088533825</v>
+        <v>0.5367247826720412</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6243849254528677</v>
+        <v>0.5275979796998689</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5926297897139527</v>
+        <v>0.5275979796998689</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5838162303919188</v>
+        <v>0.5304633092127629</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6380015540770239</v>
+        <v>0.5304633092127629</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6356286727210918</v>
+        <v>0.5336676217765043</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6384172696809286</v>
+        <v>0.5508595988538681</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6486314409207906</v>
+        <v>0.5494269340974212</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6498081686173571</v>
+        <v>0.5472779369627507</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6493924530134525</v>
+        <v>0.5451289398280802</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6480365208100627</v>
+        <v>0.5351002865329513</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6480365208100627</v>
+        <v>0.5308022922636103</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6566835025010928</v>
+        <v>0.5530085959885387</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6590311301053858</v>
+        <v>0.5479942693409742</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6223762808994221</v>
+        <v>0.5598713029964548</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.632244670001457</v>
+        <v>0.5390976640279734</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6666101694915254</v>
+        <v>0.5390976640279734</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6719955320285562</v>
+        <v>0.5438113739012189</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6719955320285562</v>
+        <v>0.5441503569520665</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6542853673935214</v>
+        <v>0.5069010732844447</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6902875042494294</v>
+        <v>0.5251867320674081</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.7075625273177601</v>
+        <v>0.5316337234714196</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7082021271429265</v>
+        <v>0.4986824340731387</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6697056966635908</v>
+        <v>0.4996610169491525</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6648836870477393</v>
+        <v>0.4993220338983051</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6268976737409548</v>
+        <v>0.4983050847457627</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5819654217862174</v>
+        <v>0.4980044679714438</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5722694381040261</v>
+        <v>0.4946913700160264</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5578723714244087</v>
+        <v>0.4946913700160264</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5423879364771017</v>
+        <v>0.494352386965179</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5292317031712884</v>
+        <v>0.5158423583118839</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5212301490942645</v>
+        <v>0.5157398863581176</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5069229274925938</v>
+        <v>0.5217007430430771</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5157801952309261</v>
+        <v>0.5320426399883444</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5141236462532175</v>
+        <v>0.5356243018794619</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4863654023602545</v>
+        <v>0.5257937934048856</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4863654023602545</v>
+        <v>0.5261327764557331</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5040624544703997</v>
+        <v>0.5261327764557331</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5142766257102618</v>
+        <v>0.5261327764557331</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5394249915011413</v>
+        <v>0.5222184449516779</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5394249915011413</v>
+        <v>0.4486664076538293</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5278485746199796</v>
+        <v>0.4340134039143315</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5312767714049828</v>
+        <v>0.4672337428973823</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5422456412995968</v>
+        <v>0.4683274246029819</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5378262347627605</v>
+        <v>0.467540673109611</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5378262347627605</v>
+        <v>0.4939109319605653</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5091981933854597</v>
+        <v>0.4999164683599631</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5084818610072361</v>
+        <v>0.5094269340974212</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4941484143557865</v>
+        <v>0.5127463454907484</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5042538002039726</v>
+        <v>0.5894449031130105</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4948967995726288</v>
+        <v>0.5894449031130105</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.507675683551066</v>
+        <v>0.5894449031130105</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.507675683551066</v>
+        <v>0.596646593171774</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4929143800689622</v>
+        <v>0.596646593171774</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4932917293963382</v>
+        <v>0.5677184206692244</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4975897236656792</v>
+        <v>0.5593973095041523</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4984915739886358</v>
+        <v>0.5605293574862804</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5126521295711719</v>
+        <v>0.5625632557913651</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5126521295711719</v>
+        <v>0.5830489048613472</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4713287358554709</v>
+        <v>0.5830489048613472</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5272162595308629</v>
+        <v>0.5819547375066777</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5268704773930357</v>
+        <v>0.5819547375066777</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5160167063280073</v>
+        <v>0.5865786023019766</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5147375066776747</v>
+        <v>0.6151925598562479</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.523890049050556</v>
+        <v>0.6151925598562479</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5021252003302413</v>
+        <v>0.6216395512602593</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4840692535573795</v>
+        <v>0.6178981108251178</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4799951435093002</v>
+        <v>0.6171817784468943</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4988946627167209</v>
+        <v>0.4900199116118693</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4981783303384974</v>
+        <v>0.4900199116118693</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4969501238405128</v>
+        <v>0.4959040357437715</v>
       </c>
     </row>
   </sheetData>
